--- a/templates/Strukturvorlage_DataDictionary_KBOB_FM_v0.9.5.xlsx
+++ b/templates/Strukturvorlage_DataDictionary_KBOB_FM_v0.9.5.xlsx
@@ -1952,7 +1952,6 @@
       </c>
       <c r="C1" s="45" t="n"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="B3" s="40" t="inlineStr">
         <is>
@@ -19431,7 +19430,11 @@
           <t>DictionaryCode</t>
         </is>
       </c>
-      <c r="B5" s="218" t="n"/>
+      <c r="B5" s="218" t="inlineStr">
+        <is>
+          <t>kbob_fm_data_dictionary</t>
+        </is>
+      </c>
       <c r="C5" s="221" t="inlineStr">
         <is>
           <t>SYSTEM-GENERATED</t>
@@ -19544,7 +19547,11 @@
           <t>DictionaryUri</t>
         </is>
       </c>
-      <c r="B11" s="218" t="n"/>
+      <c r="B11" s="218" t="inlineStr">
+        <is>
+          <t>https://lindas.admin.ch/KBOB/kbob_fm_data_dictionary</t>
+        </is>
+      </c>
       <c r="C11" s="221" t="inlineStr">
         <is>
           <t>SYSTEM-GENERATED</t>
@@ -20973,7 +20980,11 @@
           <t>https://www.kbob.admin.ch/class/grundstuck</t>
         </is>
       </c>
-      <c r="I7" s="52" t="n"/>
+      <c r="I7" s="52" t="inlineStr">
+        <is>
+          <t>site</t>
+        </is>
+      </c>
       <c r="J7" s="52" t="inlineStr">
         <is>
           <t>grundstuck</t>
@@ -20984,17 +20995,20 @@
           <t>Spatial structure</t>
         </is>
       </c>
-      <c r="L7" s="240">
-        <f>IFERROR(INDEX(Rules!$B:$B,MATCH(K8,Rules!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="M7" s="240">
-        <f>IFERROR(INDEX(Rules!$C:$C,MATCH(K8,Rules!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="N7" s="240">
-        <f>IFERROR(INDEX(Rules!$D:$D,MATCH(K8,Rules!$A:$A,0)),"")</f>
-        <v/>
+      <c r="L7" s="240" t="inlineStr">
+        <is>
+          <t>Räumliche Struktur</t>
+        </is>
+      </c>
+      <c r="M7" s="240" t="inlineStr">
+        <is>
+          <t>Structure spatiale</t>
+        </is>
+      </c>
+      <c r="N7" s="240" t="inlineStr">
+        <is>
+          <t>Struttura spaziale</t>
+        </is>
       </c>
       <c r="O7" s="58" t="inlineStr">
         <is>
@@ -21074,7 +21088,11 @@
           <t>https://www.kbob.admin.ch/class/gebaude</t>
         </is>
       </c>
-      <c r="I8" s="52" t="n"/>
+      <c r="I8" s="52" t="inlineStr">
+        <is>
+          <t>building</t>
+        </is>
+      </c>
       <c r="J8" s="52" t="inlineStr">
         <is>
           <t>gebaude</t>
@@ -21085,17 +21103,20 @@
           <t>Spatial structure</t>
         </is>
       </c>
-      <c r="L8" s="240">
-        <f>IFERROR(INDEX(Rules!$B:$B,MATCH(K9,Rules!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="M8" s="240">
-        <f>IFERROR(INDEX(Rules!$C:$C,MATCH(K9,Rules!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="N8" s="240">
-        <f>IFERROR(INDEX(Rules!$D:$D,MATCH(K9,Rules!$A:$A,0)),"")</f>
-        <v/>
+      <c r="L8" s="240" t="inlineStr">
+        <is>
+          <t>Räumliche Struktur</t>
+        </is>
+      </c>
+      <c r="M8" s="240" t="inlineStr">
+        <is>
+          <t>Structure spatiale</t>
+        </is>
+      </c>
+      <c r="N8" s="240" t="inlineStr">
+        <is>
+          <t>Struttura spaziale</t>
+        </is>
       </c>
       <c r="O8" s="58" t="inlineStr">
         <is>
@@ -21175,7 +21196,11 @@
           <t>https://www.kbob.admin.ch/class/geschoss</t>
         </is>
       </c>
-      <c r="I9" s="52" t="n"/>
+      <c r="I9" s="52" t="inlineStr">
+        <is>
+          <t>storey</t>
+        </is>
+      </c>
       <c r="J9" s="52" t="inlineStr">
         <is>
           <t>geschoss</t>
@@ -21186,17 +21211,20 @@
           <t>Spatial structure</t>
         </is>
       </c>
-      <c r="L9" s="240">
-        <f>IFERROR(INDEX(Rules!$B:$B,MATCH(K10,Rules!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="M9" s="240">
-        <f>IFERROR(INDEX(Rules!$C:$C,MATCH(K10,Rules!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="N9" s="240">
-        <f>IFERROR(INDEX(Rules!$D:$D,MATCH(K10,Rules!$A:$A,0)),"")</f>
-        <v/>
+      <c r="L9" s="240" t="inlineStr">
+        <is>
+          <t>Räumliche Struktur</t>
+        </is>
+      </c>
+      <c r="M9" s="240" t="inlineStr">
+        <is>
+          <t>Structure spatiale</t>
+        </is>
+      </c>
+      <c r="N9" s="240" t="inlineStr">
+        <is>
+          <t>Struttura spaziale</t>
+        </is>
       </c>
       <c r="O9" s="58" t="inlineStr">
         <is>
@@ -21276,7 +21304,11 @@
           <t>https://www.kbob.admin.ch/class/raum</t>
         </is>
       </c>
-      <c r="I10" s="52" t="n"/>
+      <c r="I10" s="52" t="inlineStr">
+        <is>
+          <t>room</t>
+        </is>
+      </c>
       <c r="J10" s="52" t="inlineStr">
         <is>
           <t>raum</t>
@@ -21287,17 +21319,20 @@
           <t>Spatial structure</t>
         </is>
       </c>
-      <c r="L10" s="240">
-        <f>IFERROR(INDEX(Rules!$B:$B,MATCH(K11,Rules!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="M10" s="240">
-        <f>IFERROR(INDEX(Rules!$C:$C,MATCH(K11,Rules!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="N10" s="240">
-        <f>IFERROR(INDEX(Rules!$D:$D,MATCH(K11,Rules!$A:$A,0)),"")</f>
-        <v/>
+      <c r="L10" s="240" t="inlineStr">
+        <is>
+          <t>Räumliche Struktur</t>
+        </is>
+      </c>
+      <c r="M10" s="240" t="inlineStr">
+        <is>
+          <t>Structure spatiale</t>
+        </is>
+      </c>
+      <c r="N10" s="240" t="inlineStr">
+        <is>
+          <t>Struttura spaziale</t>
+        </is>
       </c>
       <c r="O10" s="61" t="inlineStr">
         <is>
@@ -21377,7 +21412,11 @@
           <t>https://www.kbob.admin.ch/class/bauteil</t>
         </is>
       </c>
-      <c r="I11" s="52" t="n"/>
+      <c r="I11" s="52" t="inlineStr">
+        <is>
+          <t>component</t>
+        </is>
+      </c>
       <c r="J11" s="52" t="inlineStr">
         <is>
           <t>bauteil</t>
@@ -21388,17 +21427,20 @@
           <t>Physical elements</t>
         </is>
       </c>
-      <c r="L11" s="240">
-        <f>IFERROR(INDEX(Rules!$B:$B,MATCH(K12,Rules!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="M11" s="240">
-        <f>IFERROR(INDEX(Rules!$C:$C,MATCH(K12,Rules!$A:$A,0)),"")</f>
-        <v/>
-      </c>
-      <c r="N11" s="240">
-        <f>IFERROR(INDEX(Rules!$D:$D,MATCH(K12,Rules!$A:$A,0)),"")</f>
-        <v/>
+      <c r="L11" s="240" t="inlineStr">
+        <is>
+          <t>Physische Bauteile</t>
+        </is>
+      </c>
+      <c r="M11" s="240" t="inlineStr">
+        <is>
+          <t>Éléments physiques</t>
+        </is>
+      </c>
+      <c r="N11" s="240" t="inlineStr">
+        <is>
+          <t>Elementi fisici</t>
+        </is>
       </c>
       <c r="O11" s="58" t="inlineStr">
         <is>
@@ -22714,7 +22756,11 @@
       <c r="A7" s="105" t="n"/>
       <c r="C7" s="105" t="n"/>
       <c r="D7" s="55" t="n"/>
-      <c r="E7" s="55" t="n"/>
+      <c r="E7" s="55" t="inlineStr">
+        <is>
+          <t>guid</t>
+        </is>
+      </c>
       <c r="F7" s="55" t="inlineStr">
         <is>
           <t>guid</t>
@@ -22802,7 +22848,11 @@
       <c r="A8" s="105" t="n"/>
       <c r="C8" s="105" t="n"/>
       <c r="D8" s="55" t="n"/>
-      <c r="E8" s="55" t="n"/>
+      <c r="E8" s="55" t="inlineStr">
+        <is>
+          <t>site-id</t>
+        </is>
+      </c>
       <c r="F8" s="55" t="inlineStr">
         <is>
           <t>grundstuck-id</t>
@@ -22894,7 +22944,11 @@
       <c r="A9" s="105" t="n"/>
       <c r="C9" s="105" t="n"/>
       <c r="D9" s="120" t="n"/>
-      <c r="E9" s="120" t="n"/>
+      <c r="E9" s="120" t="inlineStr">
+        <is>
+          <t>economic-unit-id</t>
+        </is>
+      </c>
       <c r="F9" s="55" t="inlineStr">
         <is>
           <t>wirtschaftseinheit-id</t>
@@ -22986,7 +23040,11 @@
       <c r="A10" s="105" t="n"/>
       <c r="C10" s="105" t="n"/>
       <c r="D10" s="120" t="n"/>
-      <c r="E10" s="120" t="n"/>
+      <c r="E10" s="120" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
       <c r="F10" s="55" t="inlineStr">
         <is>
           <t>ort</t>
@@ -23078,7 +23136,11 @@
       <c r="A11" s="105" t="n"/>
       <c r="C11" s="105" t="n"/>
       <c r="D11" s="120" t="n"/>
-      <c r="E11" s="120" t="n"/>
+      <c r="E11" s="120" t="inlineStr">
+        <is>
+          <t>designation</t>
+        </is>
+      </c>
       <c r="F11" s="55" t="inlineStr">
         <is>
           <t>bezeichnung</t>
@@ -23166,7 +23228,11 @@
       <c r="A12" s="105" t="n"/>
       <c r="C12" s="105" t="n"/>
       <c r="D12" s="120" t="n"/>
-      <c r="E12" s="120" t="n"/>
+      <c r="E12" s="120" t="inlineStr">
+        <is>
+          <t>country-code</t>
+        </is>
+      </c>
       <c r="F12" s="55" t="inlineStr">
         <is>
           <t>landeskurzel</t>
@@ -23258,7 +23324,11 @@
       <c r="A13" s="105" t="n"/>
       <c r="C13" s="105" t="n"/>
       <c r="D13" s="120" t="n"/>
-      <c r="E13" s="120" t="n"/>
+      <c r="E13" s="120" t="inlineStr">
+        <is>
+          <t>canton</t>
+        </is>
+      </c>
       <c r="F13" s="55" t="inlineStr">
         <is>
           <t>kanton</t>
@@ -23350,7 +23420,11 @@
       <c r="A14" s="105" t="n"/>
       <c r="C14" s="105" t="n"/>
       <c r="D14" s="120" t="n"/>
-      <c r="E14" s="120" t="n"/>
+      <c r="E14" s="120" t="inlineStr">
+        <is>
+          <t>postal-code</t>
+        </is>
+      </c>
       <c r="F14" s="55" t="inlineStr">
         <is>
           <t>postleitzahl</t>
@@ -23442,7 +23516,11 @@
       <c r="A15" s="105" t="n"/>
       <c r="C15" s="105" t="n"/>
       <c r="D15" s="120" t="n"/>
-      <c r="E15" s="120" t="n"/>
+      <c r="E15" s="120" t="inlineStr">
+        <is>
+          <t>political-municipality</t>
+        </is>
+      </c>
       <c r="F15" s="55" t="inlineStr">
         <is>
           <t>politische-gemeinde</t>
@@ -23534,7 +23612,11 @@
       <c r="A16" s="105" t="n"/>
       <c r="C16" s="105" t="n"/>
       <c r="D16" s="120" t="n"/>
-      <c r="E16" s="120" t="n"/>
+      <c r="E16" s="120" t="inlineStr">
+        <is>
+          <t>gis-parcel-number</t>
+        </is>
+      </c>
       <c r="F16" s="55" t="inlineStr">
         <is>
           <t>gis-parzellennummer</t>
@@ -23626,7 +23708,11 @@
       <c r="A17" s="105" t="n"/>
       <c r="C17" s="105" t="n"/>
       <c r="D17" s="120" t="n"/>
-      <c r="E17" s="120" t="n"/>
+      <c r="E17" s="120" t="inlineStr">
+        <is>
+          <t>site-area</t>
+        </is>
+      </c>
       <c r="F17" s="55" t="inlineStr">
         <is>
           <t>grundstucksflache</t>
@@ -23701,10 +23787,26 @@
           <t>http://qudt.org/vocab/unit/M2</t>
         </is>
       </c>
-      <c r="AA17" s="53" t="n"/>
-      <c r="AB17" s="53" t="n"/>
-      <c r="AC17" s="53" t="n"/>
-      <c r="AD17" s="53" t="n"/>
+      <c r="AA17" s="53" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="AB17" s="53" t="inlineStr">
+        <is>
+          <t>quadratmeter</t>
+        </is>
+      </c>
+      <c r="AC17" s="53" t="inlineStr">
+        <is>
+          <t>mètre carré</t>
+        </is>
+      </c>
+      <c r="AD17" s="53" t="inlineStr">
+        <is>
+          <t>metro quadrato</t>
+        </is>
+      </c>
       <c r="AE17" s="105" t="n"/>
       <c r="AF17" s="54" t="inlineStr">
         <is>
@@ -23726,7 +23828,11 @@
       <c r="A18" s="105" t="n"/>
       <c r="C18" s="105" t="n"/>
       <c r="D18" s="120" t="n"/>
-      <c r="E18" s="120" t="n"/>
+      <c r="E18" s="120" t="inlineStr">
+        <is>
+          <t>owner-entity</t>
+        </is>
+      </c>
       <c r="F18" s="55" t="inlineStr">
         <is>
           <t>eigentumerin</t>
@@ -23810,7 +23916,11 @@
       <c r="A19" s="105" t="n"/>
       <c r="C19" s="105" t="n"/>
       <c r="D19" s="120" t="n"/>
-      <c r="E19" s="120" t="n"/>
+      <c r="E19" s="120" t="inlineStr">
+        <is>
+          <t>easement-id</t>
+        </is>
+      </c>
       <c r="F19" s="55" t="inlineStr">
         <is>
           <t>dienstbarkeiten-id</t>
@@ -23902,7 +24012,11 @@
       <c r="A20" s="105" t="n"/>
       <c r="C20" s="105" t="n"/>
       <c r="D20" s="120" t="n"/>
-      <c r="E20" s="120" t="n"/>
+      <c r="E20" s="120" t="inlineStr">
+        <is>
+          <t>easement-name</t>
+        </is>
+      </c>
       <c r="F20" s="55" t="inlineStr">
         <is>
           <t>dienstbarkeitenname</t>
@@ -23994,7 +24108,11 @@
       <c r="A21" s="105" t="n"/>
       <c r="C21" s="105" t="n"/>
       <c r="D21" s="120" t="n"/>
-      <c r="E21" s="120" t="n"/>
+      <c r="E21" s="120" t="inlineStr">
+        <is>
+          <t>building-id</t>
+        </is>
+      </c>
       <c r="F21" s="55" t="inlineStr">
         <is>
           <t>gebaude-id</t>
@@ -24086,7 +24204,11 @@
       <c r="A22" s="105" t="n"/>
       <c r="C22" s="105" t="n"/>
       <c r="D22" s="120" t="n"/>
-      <c r="E22" s="120" t="n"/>
+      <c r="E22" s="120" t="inlineStr">
+        <is>
+          <t>object-id</t>
+        </is>
+      </c>
       <c r="F22" s="55" t="inlineStr">
         <is>
           <t>objekt-id</t>
@@ -24178,7 +24300,11 @@
       <c r="A23" s="105" t="n"/>
       <c r="C23" s="105" t="n"/>
       <c r="D23" s="120" t="n"/>
-      <c r="E23" s="120" t="n"/>
+      <c r="E23" s="120" t="inlineStr">
+        <is>
+          <t>building-designation</t>
+        </is>
+      </c>
       <c r="F23" s="55" t="inlineStr">
         <is>
           <t>gebaudebezeichnung</t>
@@ -24266,7 +24392,11 @@
       <c r="A24" s="105" t="n"/>
       <c r="C24" s="105" t="n"/>
       <c r="D24" s="120" t="n"/>
-      <c r="E24" s="120" t="n"/>
+      <c r="E24" s="120" t="inlineStr">
+        <is>
+          <t>object-type</t>
+        </is>
+      </c>
       <c r="F24" s="55" t="inlineStr">
         <is>
           <t>objekttyp</t>
@@ -24354,7 +24484,11 @@
       <c r="A25" s="105" t="n"/>
       <c r="C25" s="105" t="n"/>
       <c r="D25" s="120" t="n"/>
-      <c r="E25" s="120" t="n"/>
+      <c r="E25" s="120" t="inlineStr">
+        <is>
+          <t>street-and-house-number</t>
+        </is>
+      </c>
       <c r="F25" s="55" t="inlineStr">
         <is>
           <t>strasse-hausnummer</t>
@@ -24446,7 +24580,11 @@
       <c r="A26" s="105" t="n"/>
       <c r="C26" s="105" t="n"/>
       <c r="D26" s="120" t="n"/>
-      <c r="E26" s="120" t="n"/>
+      <c r="E26" s="120" t="inlineStr">
+        <is>
+          <t>project-references</t>
+        </is>
+      </c>
       <c r="F26" s="55" t="inlineStr">
         <is>
           <t>projektreferenzen</t>
@@ -24538,7 +24676,11 @@
       <c r="A27" s="105" t="n"/>
       <c r="C27" s="105" t="n"/>
       <c r="D27" s="120" t="n"/>
-      <c r="E27" s="120" t="n"/>
+      <c r="E27" s="120" t="inlineStr">
+        <is>
+          <t>hazard-level</t>
+        </is>
+      </c>
       <c r="F27" s="55" t="inlineStr">
         <is>
           <t>gefahrdungsstufe</t>
@@ -24630,7 +24772,11 @@
       <c r="A28" s="105" t="n"/>
       <c r="C28" s="105" t="n"/>
       <c r="D28" s="120" t="n"/>
-      <c r="E28" s="120" t="n"/>
+      <c r="E28" s="120" t="inlineStr">
+        <is>
+          <t>cost-centre</t>
+        </is>
+      </c>
       <c r="F28" s="55" t="inlineStr">
         <is>
           <t>kostentrager</t>
@@ -24714,7 +24860,11 @@
       <c r="A29" s="105" t="n"/>
       <c r="C29" s="105" t="n"/>
       <c r="D29" s="120" t="n"/>
-      <c r="E29" s="120" t="n"/>
+      <c r="E29" s="120" t="inlineStr">
+        <is>
+          <t>object-manager</t>
+        </is>
+      </c>
       <c r="F29" s="55" t="inlineStr">
         <is>
           <t>objektverantwortlicher</t>
@@ -24798,7 +24948,11 @@
       <c r="A30" s="105" t="n"/>
       <c r="C30" s="105" t="n"/>
       <c r="D30" s="120" t="n"/>
-      <c r="E30" s="120" t="n"/>
+      <c r="E30" s="120" t="inlineStr">
+        <is>
+          <t>building-footprint-area</t>
+        </is>
+      </c>
       <c r="F30" s="55" t="inlineStr">
         <is>
           <t>gebaudegrundflache</t>
@@ -24873,10 +25027,26 @@
           <t>http://qudt.org/vocab/unit/M2</t>
         </is>
       </c>
-      <c r="AA30" s="53" t="n"/>
-      <c r="AB30" s="53" t="n"/>
-      <c r="AC30" s="53" t="n"/>
-      <c r="AD30" s="53" t="n"/>
+      <c r="AA30" s="53" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="AB30" s="53" t="inlineStr">
+        <is>
+          <t>quadratmeter</t>
+        </is>
+      </c>
+      <c r="AC30" s="53" t="inlineStr">
+        <is>
+          <t>mètre carré</t>
+        </is>
+      </c>
+      <c r="AD30" s="53" t="inlineStr">
+        <is>
+          <t>metro quadrato</t>
+        </is>
+      </c>
       <c r="AE30" s="105" t="n"/>
       <c r="AF30" s="54" t="inlineStr">
         <is>
@@ -24898,7 +25068,11 @@
       <c r="A31" s="105" t="n"/>
       <c r="C31" s="105" t="n"/>
       <c r="D31" s="120" t="n"/>
-      <c r="E31" s="120" t="n"/>
+      <c r="E31" s="120" t="inlineStr">
+        <is>
+          <t>building-volume</t>
+        </is>
+      </c>
       <c r="F31" s="55" t="inlineStr">
         <is>
           <t>gebaudevolumen</t>
@@ -24973,10 +25147,26 @@
           <t>http://qudt.org/vocab/unit/M3</t>
         </is>
       </c>
-      <c r="AA31" s="53" t="n"/>
-      <c r="AB31" s="53" t="n"/>
-      <c r="AC31" s="53" t="n"/>
-      <c r="AD31" s="53" t="n"/>
+      <c r="AA31" s="53" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="AB31" s="53" t="inlineStr">
+        <is>
+          <t>kubikmeter</t>
+        </is>
+      </c>
+      <c r="AC31" s="53" t="inlineStr">
+        <is>
+          <t>mètre cube</t>
+        </is>
+      </c>
+      <c r="AD31" s="53" t="inlineStr">
+        <is>
+          <t>metro cubo</t>
+        </is>
+      </c>
       <c r="AE31" s="105" t="n"/>
       <c r="AF31" s="54" t="inlineStr">
         <is>
@@ -24998,7 +25188,11 @@
       <c r="A32" s="105" t="n"/>
       <c r="C32" s="105" t="n"/>
       <c r="D32" s="120" t="n"/>
-      <c r="E32" s="120" t="n"/>
+      <c r="E32" s="120" t="inlineStr">
+        <is>
+          <t>building-insurance-number</t>
+        </is>
+      </c>
       <c r="F32" s="55" t="inlineStr">
         <is>
           <t>nummer-gebaudeversicherung</t>
@@ -25090,7 +25284,11 @@
       <c r="A33" s="105" t="n"/>
       <c r="C33" s="105" t="n"/>
       <c r="D33" s="120" t="n"/>
-      <c r="E33" s="120" t="n"/>
+      <c r="E33" s="120" t="inlineStr">
+        <is>
+          <t>year-of-construction</t>
+        </is>
+      </c>
       <c r="F33" s="55" t="inlineStr">
         <is>
           <t>baujahr</t>
@@ -25182,7 +25380,11 @@
       <c r="A34" s="105" t="n"/>
       <c r="C34" s="105" t="n"/>
       <c r="D34" s="120" t="n"/>
-      <c r="E34" s="120" t="n"/>
+      <c r="E34" s="120" t="inlineStr">
+        <is>
+          <t>owner</t>
+        </is>
+      </c>
       <c r="F34" s="55" t="inlineStr">
         <is>
           <t>eigentumer</t>
@@ -25266,7 +25468,11 @@
       <c r="A35" s="105" t="n"/>
       <c r="C35" s="105" t="n"/>
       <c r="D35" s="120" t="n"/>
-      <c r="E35" s="120" t="n"/>
+      <c r="E35" s="120" t="inlineStr">
+        <is>
+          <t>electrical-utility-connection</t>
+        </is>
+      </c>
       <c r="F35" s="55" t="inlineStr">
         <is>
           <t>medienbezug-elektrisch</t>
@@ -25358,7 +25564,11 @@
       <c r="A36" s="105" t="n"/>
       <c r="C36" s="105" t="n"/>
       <c r="D36" s="120" t="n"/>
-      <c r="E36" s="120" t="n"/>
+      <c r="E36" s="120" t="inlineStr">
+        <is>
+          <t>water-utility-connection</t>
+        </is>
+      </c>
       <c r="F36" s="55" t="inlineStr">
         <is>
           <t>medienbezug-wasser</t>
@@ -25450,7 +25660,11 @@
       <c r="A37" s="105" t="n"/>
       <c r="C37" s="105" t="n"/>
       <c r="D37" s="120" t="n"/>
-      <c r="E37" s="120" t="n"/>
+      <c r="E37" s="120" t="inlineStr">
+        <is>
+          <t>heating-utility-connection</t>
+        </is>
+      </c>
       <c r="F37" s="55" t="inlineStr">
         <is>
           <t>medienbezug-heizung</t>
@@ -25542,7 +25756,11 @@
       <c r="A38" s="105" t="n"/>
       <c r="C38" s="105" t="n"/>
       <c r="D38" s="120" t="n"/>
-      <c r="E38" s="120" t="n"/>
+      <c r="E38" s="120" t="inlineStr">
+        <is>
+          <t>outdoor-use-type</t>
+        </is>
+      </c>
       <c r="F38" s="55" t="inlineStr">
         <is>
           <t>nutzungsart-aussen</t>
@@ -25634,7 +25852,11 @@
       <c r="A39" s="105" t="n"/>
       <c r="C39" s="105" t="n"/>
       <c r="D39" s="120" t="n"/>
-      <c r="E39" s="120" t="n"/>
+      <c r="E39" s="120" t="inlineStr">
+        <is>
+          <t>building-class</t>
+        </is>
+      </c>
       <c r="F39" s="55" t="inlineStr">
         <is>
           <t>gebaudeklasse</t>
@@ -25726,7 +25948,11 @@
       <c r="A40" s="105" t="n"/>
       <c r="C40" s="105" t="n"/>
       <c r="D40" s="120" t="n"/>
-      <c r="E40" s="120" t="n"/>
+      <c r="E40" s="120" t="inlineStr">
+        <is>
+          <t>building-label</t>
+        </is>
+      </c>
       <c r="F40" s="55" t="inlineStr">
         <is>
           <t>gebaudelabel</t>
@@ -25818,7 +26044,11 @@
       <c r="A41" s="105" t="n"/>
       <c r="C41" s="105" t="n"/>
       <c r="D41" s="120" t="n"/>
-      <c r="E41" s="120" t="n"/>
+      <c r="E41" s="120" t="inlineStr">
+        <is>
+          <t>sustainability-certification</t>
+        </is>
+      </c>
       <c r="F41" s="55" t="inlineStr">
         <is>
           <t>nachhaltigkeitsnachweis</t>
@@ -25902,7 +26132,11 @@
       <c r="A42" s="105" t="n"/>
       <c r="C42" s="105" t="n"/>
       <c r="D42" s="120" t="n"/>
-      <c r="E42" s="120" t="n"/>
+      <c r="E42" s="120" t="inlineStr">
+        <is>
+          <t>heritage-status</t>
+        </is>
+      </c>
       <c r="F42" s="55" t="inlineStr">
         <is>
           <t>denkmalstatus</t>
@@ -25994,7 +26228,11 @@
       <c r="A43" s="105" t="n"/>
       <c r="C43" s="105" t="n"/>
       <c r="D43" s="120" t="n"/>
-      <c r="E43" s="120" t="n"/>
+      <c r="E43" s="120" t="inlineStr">
+        <is>
+          <t>seismic-building-class</t>
+        </is>
+      </c>
       <c r="F43" s="55" t="inlineStr">
         <is>
           <t>erdbebenbauwerksklasse</t>
@@ -26086,7 +26324,11 @@
       <c r="A44" s="105" t="n"/>
       <c r="C44" s="105" t="n"/>
       <c r="D44" s="120" t="n"/>
-      <c r="E44" s="120" t="n"/>
+      <c r="E44" s="120" t="inlineStr">
+        <is>
+          <t>protection-zone</t>
+        </is>
+      </c>
       <c r="F44" s="55" t="inlineStr">
         <is>
           <t>schutzzone</t>
@@ -26170,7 +26412,11 @@
       <c r="A45" s="105" t="n"/>
       <c r="C45" s="105" t="n"/>
       <c r="D45" s="120" t="n"/>
-      <c r="E45" s="120" t="n"/>
+      <c r="E45" s="120" t="inlineStr">
+        <is>
+          <t>surrounding-area-id</t>
+        </is>
+      </c>
       <c r="F45" s="55" t="inlineStr">
         <is>
           <t>umgebungsflache-id</t>
@@ -26262,7 +26508,11 @@
       <c r="A46" s="105" t="n"/>
       <c r="C46" s="105" t="n"/>
       <c r="D46" s="120" t="n"/>
-      <c r="E46" s="120" t="n"/>
+      <c r="E46" s="120" t="inlineStr">
+        <is>
+          <t>surrounding-area-number</t>
+        </is>
+      </c>
       <c r="F46" s="55" t="inlineStr">
         <is>
           <t>umgebungsflachennummer</t>
@@ -26354,7 +26604,11 @@
       <c r="A47" s="105" t="n"/>
       <c r="C47" s="105" t="n"/>
       <c r="D47" s="120" t="n"/>
-      <c r="E47" s="120" t="n"/>
+      <c r="E47" s="120" t="inlineStr">
+        <is>
+          <t>storey-id</t>
+        </is>
+      </c>
       <c r="F47" s="55" t="inlineStr">
         <is>
           <t>geschoss-id</t>
@@ -26438,7 +26692,11 @@
       <c r="A48" s="105" t="n"/>
       <c r="C48" s="105" t="n"/>
       <c r="D48" s="120" t="n"/>
-      <c r="E48" s="120" t="n"/>
+      <c r="E48" s="120" t="inlineStr">
+        <is>
+          <t>storey-designation</t>
+        </is>
+      </c>
       <c r="F48" s="55" t="inlineStr">
         <is>
           <t>geschossbezeichnung</t>
@@ -26526,7 +26784,11 @@
       <c r="A49" s="105" t="n"/>
       <c r="C49" s="105" t="n"/>
       <c r="D49" s="120" t="n"/>
-      <c r="E49" s="120" t="n"/>
+      <c r="E49" s="120" t="inlineStr">
+        <is>
+          <t>storey-volume</t>
+        </is>
+      </c>
       <c r="F49" s="55" t="inlineStr">
         <is>
           <t>geschossvolumen</t>
@@ -26601,10 +26863,26 @@
           <t>http://qudt.org/vocab/unit/M3</t>
         </is>
       </c>
-      <c r="AA49" s="53" t="n"/>
-      <c r="AB49" s="53" t="n"/>
-      <c r="AC49" s="53" t="n"/>
-      <c r="AD49" s="53" t="n"/>
+      <c r="AA49" s="53" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="AB49" s="53" t="inlineStr">
+        <is>
+          <t>kubikmeter</t>
+        </is>
+      </c>
+      <c r="AC49" s="53" t="inlineStr">
+        <is>
+          <t>mètre cube</t>
+        </is>
+      </c>
+      <c r="AD49" s="53" t="inlineStr">
+        <is>
+          <t>metro cubo</t>
+        </is>
+      </c>
       <c r="AE49" s="105" t="n"/>
       <c r="AF49" s="54" t="inlineStr">
         <is>
@@ -26626,7 +26904,11 @@
       <c r="A50" s="105" t="n"/>
       <c r="C50" s="105" t="n"/>
       <c r="D50" s="120" t="n"/>
-      <c r="E50" s="120" t="n"/>
+      <c r="E50" s="120" t="inlineStr">
+        <is>
+          <t>storey-height</t>
+        </is>
+      </c>
       <c r="F50" s="55" t="inlineStr">
         <is>
           <t>geschosshohe</t>
@@ -26718,7 +27000,11 @@
       <c r="A51" s="105" t="n"/>
       <c r="C51" s="105" t="n"/>
       <c r="D51" s="120" t="n"/>
-      <c r="E51" s="120" t="n"/>
+      <c r="E51" s="120" t="inlineStr">
+        <is>
+          <t>storey-area</t>
+        </is>
+      </c>
       <c r="F51" s="55" t="inlineStr">
         <is>
           <t>geschossflache</t>
@@ -26793,10 +27079,26 @@
           <t>http://qudt.org/vocab/unit/M2</t>
         </is>
       </c>
-      <c r="AA51" s="53" t="n"/>
-      <c r="AB51" s="53" t="n"/>
-      <c r="AC51" s="53" t="n"/>
-      <c r="AD51" s="53" t="n"/>
+      <c r="AA51" s="53" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="AB51" s="53" t="inlineStr">
+        <is>
+          <t>quadratmeter</t>
+        </is>
+      </c>
+      <c r="AC51" s="53" t="inlineStr">
+        <is>
+          <t>mètre carré</t>
+        </is>
+      </c>
+      <c r="AD51" s="53" t="inlineStr">
+        <is>
+          <t>metro quadrato</t>
+        </is>
+      </c>
       <c r="AE51" s="105" t="n"/>
       <c r="AF51" s="54" t="inlineStr">
         <is>
@@ -26818,7 +27120,11 @@
       <c r="A52" s="105" t="n"/>
       <c r="C52" s="105" t="n"/>
       <c r="D52" s="120" t="n"/>
-      <c r="E52" s="120" t="n"/>
+      <c r="E52" s="120" t="inlineStr">
+        <is>
+          <t>external-storey-area</t>
+        </is>
+      </c>
       <c r="F52" s="55" t="inlineStr">
         <is>
           <t>aussengeschossflache</t>
@@ -26893,10 +27199,26 @@
           <t>http://qudt.org/vocab/unit/M2</t>
         </is>
       </c>
-      <c r="AA52" s="53" t="n"/>
-      <c r="AB52" s="53" t="n"/>
-      <c r="AC52" s="53" t="n"/>
-      <c r="AD52" s="53" t="n"/>
+      <c r="AA52" s="53" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="AB52" s="53" t="inlineStr">
+        <is>
+          <t>quadratmeter</t>
+        </is>
+      </c>
+      <c r="AC52" s="53" t="inlineStr">
+        <is>
+          <t>mètre carré</t>
+        </is>
+      </c>
+      <c r="AD52" s="53" t="inlineStr">
+        <is>
+          <t>metro quadrato</t>
+        </is>
+      </c>
       <c r="AE52" s="105" t="n"/>
       <c r="AF52" s="54" t="inlineStr">
         <is>
@@ -26918,7 +27240,11 @@
       <c r="A53" s="105" t="n"/>
       <c r="C53" s="105" t="n"/>
       <c r="D53" s="120" t="n"/>
-      <c r="E53" s="120" t="n"/>
+      <c r="E53" s="120" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
       <c r="F53" s="55" t="inlineStr">
         <is>
           <t>beschreibung</t>
@@ -27006,7 +27332,11 @@
       <c r="A54" s="105" t="n"/>
       <c r="C54" s="105" t="n"/>
       <c r="D54" s="120" t="n"/>
-      <c r="E54" s="120" t="n"/>
+      <c r="E54" s="120" t="inlineStr">
+        <is>
+          <t>above-ground</t>
+        </is>
+      </c>
       <c r="F54" s="55" t="inlineStr">
         <is>
           <t>oberirdisch</t>
@@ -27098,7 +27428,11 @@
       <c r="A55" s="105" t="n"/>
       <c r="C55" s="105" t="n"/>
       <c r="D55" s="120" t="n"/>
-      <c r="E55" s="120" t="n"/>
+      <c r="E55" s="120" t="inlineStr">
+        <is>
+          <t>room-id</t>
+        </is>
+      </c>
       <c r="F55" s="55" t="inlineStr">
         <is>
           <t>raum-id</t>
@@ -27182,7 +27516,11 @@
       <c r="A56" s="105" t="n"/>
       <c r="C56" s="105" t="n"/>
       <c r="D56" s="120" t="n"/>
-      <c r="E56" s="120" t="n"/>
+      <c r="E56" s="120" t="inlineStr">
+        <is>
+          <t>operational-room-number</t>
+        </is>
+      </c>
       <c r="F56" s="55" t="inlineStr">
         <is>
           <t>raumnummer-betrieb</t>
@@ -27266,7 +27604,11 @@
       <c r="A57" s="105" t="n"/>
       <c r="C57" s="105" t="n"/>
       <c r="D57" s="120" t="n"/>
-      <c r="E57" s="120" t="n"/>
+      <c r="E57" s="120" t="inlineStr">
+        <is>
+          <t>room-designation</t>
+        </is>
+      </c>
       <c r="F57" s="55" t="inlineStr">
         <is>
           <t>raumbezeichnung</t>
@@ -27354,7 +27696,11 @@
       <c r="A58" s="105" t="n"/>
       <c r="C58" s="105" t="n"/>
       <c r="D58" s="120" t="n"/>
-      <c r="E58" s="120" t="n"/>
+      <c r="E58" s="120" t="inlineStr">
+        <is>
+          <t>room-labelled</t>
+        </is>
+      </c>
       <c r="F58" s="55" t="inlineStr">
         <is>
           <t>raum-beschriftet</t>
@@ -27441,7 +27787,11 @@
       <c r="A59" s="105" t="n"/>
       <c r="C59" s="105" t="n"/>
       <c r="D59" s="120" t="n"/>
-      <c r="E59" s="120" t="n"/>
+      <c r="E59" s="120" t="inlineStr">
+        <is>
+          <t>room-type</t>
+        </is>
+      </c>
       <c r="F59" s="55" t="inlineStr">
         <is>
           <t>raumtyp</t>
@@ -27530,7 +27880,11 @@
     </row>
     <row r="60" ht="13.5" customFormat="1" customHeight="1" s="68">
       <c r="D60" s="55" t="n"/>
-      <c r="E60" s="55" t="n"/>
+      <c r="E60" s="55" t="inlineStr">
+        <is>
+          <t>cleaning-group</t>
+        </is>
+      </c>
       <c r="F60" s="55" t="inlineStr">
         <is>
           <t>reinigungsgruppe</t>
@@ -27610,7 +27964,11 @@
     </row>
     <row r="61" ht="13.5" customHeight="1" s="229">
       <c r="D61" s="55" t="n"/>
-      <c r="E61" s="55" t="n"/>
+      <c r="E61" s="55" t="inlineStr">
+        <is>
+          <t>area-type-sia-416</t>
+        </is>
+      </c>
       <c r="F61" s="55" t="inlineStr">
         <is>
           <t>flachenart-sia-416</t>
@@ -27694,7 +28052,11 @@
     </row>
     <row r="62" ht="13.5" customHeight="1" s="229">
       <c r="D62" s="55" t="n"/>
-      <c r="E62" s="55" t="n"/>
+      <c r="E62" s="55" t="inlineStr">
+        <is>
+          <t>area-type-d0165</t>
+        </is>
+      </c>
       <c r="F62" s="55" t="inlineStr">
         <is>
           <t>flachenart-d0165</t>
@@ -27778,7 +28140,11 @@
     </row>
     <row r="63" ht="13.5" customHeight="1" s="229">
       <c r="D63" s="55" t="n"/>
-      <c r="E63" s="55" t="n"/>
+      <c r="E63" s="55" t="inlineStr">
+        <is>
+          <t>net-room-volume</t>
+        </is>
+      </c>
       <c r="F63" s="55" t="inlineStr">
         <is>
           <t>raumvolumen-netto</t>
@@ -27852,10 +28218,26 @@
           <t>http://qudt.org/vocab/unit/M3</t>
         </is>
       </c>
-      <c r="AA63" s="119" t="n"/>
-      <c r="AB63" s="53" t="n"/>
-      <c r="AC63" s="119" t="n"/>
-      <c r="AD63" s="53" t="n"/>
+      <c r="AA63" s="119" t="inlineStr">
+        <is>
+          <t>cubic meter</t>
+        </is>
+      </c>
+      <c r="AB63" s="53" t="inlineStr">
+        <is>
+          <t>kubikmeter</t>
+        </is>
+      </c>
+      <c r="AC63" s="119" t="inlineStr">
+        <is>
+          <t>mètre cube</t>
+        </is>
+      </c>
+      <c r="AD63" s="53" t="inlineStr">
+        <is>
+          <t>metro cubo</t>
+        </is>
+      </c>
       <c r="AF63" s="53" t="inlineStr">
         <is>
           <t>Candidate</t>
@@ -27874,7 +28256,11 @@
     </row>
     <row r="64" ht="13.5" customHeight="1" s="229">
       <c r="D64" s="55" t="n"/>
-      <c r="E64" s="55" t="n"/>
+      <c r="E64" s="55" t="inlineStr">
+        <is>
+          <t>usable-height</t>
+        </is>
+      </c>
       <c r="F64" s="55" t="inlineStr">
         <is>
           <t>nutzhohe</t>
@@ -27962,7 +28348,11 @@
     </row>
     <row r="65" ht="13.5" customHeight="1" s="229">
       <c r="D65" s="55" t="n"/>
-      <c r="E65" s="55" t="n"/>
+      <c r="E65" s="55" t="inlineStr">
+        <is>
+          <t>clear-room-height</t>
+        </is>
+      </c>
       <c r="F65" s="55" t="inlineStr">
         <is>
           <t>lichte-raumhohe</t>
@@ -28050,7 +28440,11 @@
     </row>
     <row r="66" ht="13.5" customHeight="1" s="229">
       <c r="D66" s="55" t="n"/>
-      <c r="E66" s="55" t="n"/>
+      <c r="E66" s="55" t="inlineStr">
+        <is>
+          <t>gross-room-area</t>
+        </is>
+      </c>
       <c r="F66" s="55" t="inlineStr">
         <is>
           <t>raumflache-brutto</t>
@@ -28124,10 +28518,26 @@
           <t>http://qudt.org/vocab/unit/M2</t>
         </is>
       </c>
-      <c r="AA66" s="119" t="n"/>
-      <c r="AB66" s="53" t="n"/>
-      <c r="AC66" s="119" t="n"/>
-      <c r="AD66" s="53" t="n"/>
+      <c r="AA66" s="119" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="AB66" s="53" t="inlineStr">
+        <is>
+          <t>quadratmeter</t>
+        </is>
+      </c>
+      <c r="AC66" s="119" t="inlineStr">
+        <is>
+          <t>mètre carré</t>
+        </is>
+      </c>
+      <c r="AD66" s="53" t="inlineStr">
+        <is>
+          <t>metro quadrato</t>
+        </is>
+      </c>
       <c r="AF66" s="53" t="inlineStr">
         <is>
           <t>Candidate</t>
@@ -28146,7 +28556,11 @@
     </row>
     <row r="67" ht="13.5" customHeight="1" s="229">
       <c r="D67" s="55" t="n"/>
-      <c r="E67" s="55" t="n"/>
+      <c r="E67" s="55" t="inlineStr">
+        <is>
+          <t>net-room-area</t>
+        </is>
+      </c>
       <c r="F67" s="55" t="inlineStr">
         <is>
           <t>raumflache-netto</t>
@@ -28220,10 +28634,26 @@
           <t>http://qudt.org/vocab/unit/M2</t>
         </is>
       </c>
-      <c r="AA67" s="119" t="n"/>
-      <c r="AB67" s="53" t="n"/>
-      <c r="AC67" s="119" t="n"/>
-      <c r="AD67" s="53" t="n"/>
+      <c r="AA67" s="119" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="AB67" s="53" t="inlineStr">
+        <is>
+          <t>quadratmeter</t>
+        </is>
+      </c>
+      <c r="AC67" s="119" t="inlineStr">
+        <is>
+          <t>mètre carré</t>
+        </is>
+      </c>
+      <c r="AD67" s="53" t="inlineStr">
+        <is>
+          <t>metro quadrato</t>
+        </is>
+      </c>
       <c r="AF67" s="53" t="inlineStr">
         <is>
           <t>Candidate</t>
@@ -28242,7 +28672,11 @@
     </row>
     <row r="68" ht="13.5" customHeight="1" s="229">
       <c r="D68" s="55" t="n"/>
-      <c r="E68" s="55" t="n"/>
+      <c r="E68" s="55" t="inlineStr">
+        <is>
+          <t>area-load</t>
+        </is>
+      </c>
       <c r="F68" s="55" t="inlineStr">
         <is>
           <t>flachenlast</t>
@@ -28334,7 +28768,11 @@
     </row>
     <row r="69" ht="13.5" customHeight="1" s="229">
       <c r="D69" s="55" t="n"/>
-      <c r="E69" s="55" t="n"/>
+      <c r="E69" s="55" t="inlineStr">
+        <is>
+          <t>point-load</t>
+        </is>
+      </c>
       <c r="F69" s="55" t="inlineStr">
         <is>
           <t>punktlast</t>
@@ -28408,10 +28846,26 @@
           <t>http://qudt.org/vocab/unit/KiloN</t>
         </is>
       </c>
-      <c r="AA69" s="119" t="n"/>
-      <c r="AB69" s="53" t="n"/>
-      <c r="AC69" s="119" t="n"/>
-      <c r="AD69" s="53" t="n"/>
+      <c r="AA69" s="119" t="inlineStr">
+        <is>
+          <t>kilonewton</t>
+        </is>
+      </c>
+      <c r="AB69" s="53" t="inlineStr">
+        <is>
+          <t>kilonewton</t>
+        </is>
+      </c>
+      <c r="AC69" s="119" t="inlineStr">
+        <is>
+          <t>kilonewton</t>
+        </is>
+      </c>
+      <c r="AD69" s="53" t="inlineStr">
+        <is>
+          <t>chilonewton</t>
+        </is>
+      </c>
       <c r="AF69" s="53" t="inlineStr">
         <is>
           <t>Candidate</t>
@@ -28430,7 +28884,11 @@
     </row>
     <row r="70" ht="13.5" customHeight="1" s="229">
       <c r="D70" s="55" t="n"/>
-      <c r="E70" s="55" t="n"/>
+      <c r="E70" s="55" t="inlineStr">
+        <is>
+          <t>planned-occupancy</t>
+        </is>
+      </c>
       <c r="F70" s="55" t="inlineStr">
         <is>
           <t>personenbelegung-geplant</t>
@@ -28518,7 +28976,11 @@
     </row>
     <row r="71" ht="13.5" customHeight="1" s="229">
       <c r="D71" s="55" t="n"/>
-      <c r="E71" s="55" t="n"/>
+      <c r="E71" s="55" t="inlineStr">
+        <is>
+          <t>actual-occupancy</t>
+        </is>
+      </c>
       <c r="F71" s="55" t="inlineStr">
         <is>
           <t>personenbelegung-ist</t>
@@ -28606,7 +29068,11 @@
     </row>
     <row r="72" ht="13.5" customHeight="1" s="229">
       <c r="D72" s="55" t="n"/>
-      <c r="E72" s="55" t="n"/>
+      <c r="E72" s="55" t="inlineStr">
+        <is>
+          <t>energy-reference-area</t>
+        </is>
+      </c>
       <c r="F72" s="55" t="inlineStr">
         <is>
           <t>energiebezugsflache</t>
@@ -28694,7 +29160,11 @@
     </row>
     <row r="73" ht="13.5" customHeight="1" s="229">
       <c r="D73" s="55" t="n"/>
-      <c r="E73" s="55" t="n"/>
+      <c r="E73" s="55" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
       <c r="F73" s="55" t="inlineStr">
         <is>
           <t>temperatur</t>
@@ -28782,7 +29252,11 @@
     </row>
     <row r="74" ht="13.5" customHeight="1" s="229">
       <c r="D74" s="55" t="n"/>
-      <c r="E74" s="55" t="n"/>
+      <c r="E74" s="55" t="inlineStr">
+        <is>
+          <t>escape-route</t>
+        </is>
+      </c>
       <c r="F74" s="55" t="inlineStr">
         <is>
           <t>fluchtweg</t>
@@ -28862,7 +29336,11 @@
     </row>
     <row r="75" ht="13.5" customHeight="1" s="229">
       <c r="D75" s="55" t="n"/>
-      <c r="E75" s="55" t="n"/>
+      <c r="E75" s="55" t="inlineStr">
+        <is>
+          <t>window-area</t>
+        </is>
+      </c>
       <c r="F75" s="55" t="inlineStr">
         <is>
           <t>fensterflache</t>
@@ -28928,10 +29406,26 @@
           <t>http://qudt.org/vocab/unit/M2</t>
         </is>
       </c>
-      <c r="AA75" s="119" t="n"/>
-      <c r="AB75" s="53" t="n"/>
-      <c r="AC75" s="119" t="n"/>
-      <c r="AD75" s="53" t="n"/>
+      <c r="AA75" s="119" t="inlineStr">
+        <is>
+          <t>square meter</t>
+        </is>
+      </c>
+      <c r="AB75" s="53" t="inlineStr">
+        <is>
+          <t>quadratmeter</t>
+        </is>
+      </c>
+      <c r="AC75" s="119" t="inlineStr">
+        <is>
+          <t>mètre carré</t>
+        </is>
+      </c>
+      <c r="AD75" s="53" t="inlineStr">
+        <is>
+          <t>metro quadrato</t>
+        </is>
+      </c>
       <c r="AF75" s="53" t="inlineStr">
         <is>
           <t>Candidate</t>
@@ -28950,7 +29444,11 @@
     </row>
     <row r="76" ht="13.5" customHeight="1" s="229">
       <c r="D76" s="55" t="n"/>
-      <c r="E76" s="55" t="n"/>
+      <c r="E76" s="55" t="inlineStr">
+        <is>
+          <t>openable-window</t>
+        </is>
+      </c>
       <c r="F76" s="55" t="inlineStr">
         <is>
           <t>fenster-offenbar</t>
@@ -29034,7 +29532,11 @@
     </row>
     <row r="77" ht="13.5" customHeight="1" s="229">
       <c r="D77" s="55" t="n"/>
-      <c r="E77" s="55" t="n"/>
+      <c r="E77" s="55" t="inlineStr">
+        <is>
+          <t>room-user</t>
+        </is>
+      </c>
       <c r="F77" s="55" t="inlineStr">
         <is>
           <t>raumnutzer</t>
@@ -29122,7 +29624,11 @@
     </row>
     <row r="78" ht="13.5" customHeight="1" s="229">
       <c r="D78" s="55" t="n"/>
-      <c r="E78" s="55" t="n"/>
+      <c r="E78" s="55" t="inlineStr">
+        <is>
+          <t>floor-covering</t>
+        </is>
+      </c>
       <c r="F78" s="55" t="inlineStr">
         <is>
           <t>bodenbelag</t>
@@ -29210,7 +29716,11 @@
     </row>
     <row r="79" ht="13.5" customHeight="1" s="229">
       <c r="D79" s="55" t="n"/>
-      <c r="E79" s="55" t="n"/>
+      <c r="E79" s="55" t="inlineStr">
+        <is>
+          <t>ceiling-material</t>
+        </is>
+      </c>
       <c r="F79" s="55" t="inlineStr">
         <is>
           <t>deckenmaterial</t>
@@ -29298,7 +29808,11 @@
     </row>
     <row r="80" ht="13.5" customHeight="1" s="229">
       <c r="D80" s="55" t="n"/>
-      <c r="E80" s="55" t="n"/>
+      <c r="E80" s="55" t="inlineStr">
+        <is>
+          <t>wall-covering</t>
+        </is>
+      </c>
       <c r="F80" s="55" t="inlineStr">
         <is>
           <t>wandbelag</t>
@@ -29386,7 +29900,11 @@
     </row>
     <row r="81" ht="13.5" customHeight="1" s="229">
       <c r="D81" s="55" t="n"/>
-      <c r="E81" s="55" t="n"/>
+      <c r="E81" s="55" t="inlineStr">
+        <is>
+          <t>air-change-rate</t>
+        </is>
+      </c>
       <c r="F81" s="55" t="inlineStr">
         <is>
           <t>luftwechselrate</t>
@@ -29474,7 +29992,11 @@
     </row>
     <row r="82" ht="13.5" customHeight="1" s="229">
       <c r="D82" s="55" t="n"/>
-      <c r="E82" s="55" t="n"/>
+      <c r="E82" s="55" t="inlineStr">
+        <is>
+          <t>solar-shading</t>
+        </is>
+      </c>
       <c r="F82" s="55" t="inlineStr">
         <is>
           <t>sonnenschutz</t>
@@ -29554,7 +30076,11 @@
     </row>
     <row r="83" ht="13.5" customHeight="1" s="229">
       <c r="D83" s="55" t="n"/>
-      <c r="E83" s="55" t="n"/>
+      <c r="E83" s="55" t="inlineStr">
+        <is>
+          <t>ventilation</t>
+        </is>
+      </c>
       <c r="F83" s="55" t="inlineStr">
         <is>
           <t>beluftung</t>
@@ -29646,7 +30172,11 @@
     </row>
     <row r="84" ht="13.5" customHeight="1" s="229">
       <c r="D84" s="55" t="n"/>
-      <c r="E84" s="55" t="n"/>
+      <c r="E84" s="55" t="inlineStr">
+        <is>
+          <t>air-conditioned</t>
+        </is>
+      </c>
       <c r="F84" s="55" t="inlineStr">
         <is>
           <t>klimatisiert</t>
@@ -29730,7 +30260,11 @@
     </row>
     <row r="85" ht="13.5" customHeight="1" s="229">
       <c r="D85" s="55" t="n"/>
-      <c r="E85" s="55" t="n"/>
+      <c r="E85" s="55" t="inlineStr">
+        <is>
+          <t>humidity</t>
+        </is>
+      </c>
       <c r="F85" s="55" t="inlineStr">
         <is>
           <t>luftfeuchtigkeit</t>
@@ -29804,7 +30338,11 @@
           <t>http://qudt.org/vocab/unit/PERCENT</t>
         </is>
       </c>
-      <c r="AA85" s="119" t="n"/>
+      <c r="AA85" s="119" t="inlineStr">
+        <is>
+          <t>percent</t>
+        </is>
+      </c>
       <c r="AB85" s="53" t="n"/>
       <c r="AC85" s="119" t="n"/>
       <c r="AD85" s="53" t="n"/>
@@ -29826,7 +30364,11 @@
     </row>
     <row r="86" ht="13.5" customHeight="1" s="229">
       <c r="D86" s="55" t="n"/>
-      <c r="E86" s="55" t="n"/>
+      <c r="E86" s="55" t="inlineStr">
+        <is>
+          <t>humidified</t>
+        </is>
+      </c>
       <c r="F86" s="55" t="inlineStr">
         <is>
           <t>befeuchtet</t>
@@ -29914,7 +30456,11 @@
     </row>
     <row r="87" ht="13.5" customHeight="1" s="229">
       <c r="D87" s="55" t="n"/>
-      <c r="E87" s="55" t="n"/>
+      <c r="E87" s="55" t="inlineStr">
+        <is>
+          <t>dehumidified</t>
+        </is>
+      </c>
       <c r="F87" s="55" t="inlineStr">
         <is>
           <t>entfeuchtet</t>
@@ -30002,7 +30548,11 @@
     </row>
     <row r="88" ht="13.5" customHeight="1" s="229">
       <c r="D88" s="55" t="n"/>
-      <c r="E88" s="55" t="n"/>
+      <c r="E88" s="55" t="inlineStr">
+        <is>
+          <t>pneumatic-tube-system</t>
+        </is>
+      </c>
       <c r="F88" s="55" t="inlineStr">
         <is>
           <t>rohrpost</t>
@@ -30082,7 +30632,11 @@
     </row>
     <row r="89" ht="13.5" customHeight="1" s="229">
       <c r="D89" s="55" t="n"/>
-      <c r="E89" s="55" t="n"/>
+      <c r="E89" s="55" t="inlineStr">
+        <is>
+          <t>rentability</t>
+        </is>
+      </c>
       <c r="F89" s="55" t="inlineStr">
         <is>
           <t>vermietbarkeit</t>
@@ -30170,7 +30724,11 @@
     </row>
     <row r="90" ht="13.5" customHeight="1" s="229">
       <c r="D90" s="55" t="n"/>
-      <c r="E90" s="55" t="n"/>
+      <c r="E90" s="55" t="inlineStr">
+        <is>
+          <t>component-id</t>
+        </is>
+      </c>
       <c r="F90" s="55" t="inlineStr">
         <is>
           <t>bauteil-id</t>
@@ -30250,7 +30808,11 @@
     </row>
     <row r="91" ht="13.5" customHeight="1" s="229">
       <c r="D91" s="55" t="n"/>
-      <c r="E91" s="55" t="n"/>
+      <c r="E91" s="55" t="inlineStr">
+        <is>
+          <t>aks</t>
+        </is>
+      </c>
       <c r="F91" s="55" t="inlineStr">
         <is>
           <t>aks</t>
@@ -30338,7 +30900,11 @@
     </row>
     <row r="92" ht="13.5" customHeight="1" s="229">
       <c r="D92" s="55" t="n"/>
-      <c r="E92" s="55" t="n"/>
+      <c r="E92" s="55" t="inlineStr">
+        <is>
+          <t>drive</t>
+        </is>
+      </c>
       <c r="F92" s="55" t="inlineStr">
         <is>
           <t>antrieb</t>
@@ -30426,7 +30992,11 @@
     </row>
     <row r="93" ht="13.5" customHeight="1" s="229">
       <c r="D93" s="55" t="n"/>
-      <c r="E93" s="55" t="n"/>
+      <c r="E93" s="55" t="inlineStr">
+        <is>
+          <t>article-number</t>
+        </is>
+      </c>
       <c r="F93" s="55" t="inlineStr">
         <is>
           <t>artikelnummer</t>
@@ -30514,7 +31084,11 @@
     </row>
     <row r="94" ht="13.5" customHeight="1" s="229">
       <c r="D94" s="55" t="n"/>
-      <c r="E94" s="55" t="n"/>
+      <c r="E94" s="55" t="inlineStr">
+        <is>
+          <t>component-category</t>
+        </is>
+      </c>
       <c r="F94" s="55" t="inlineStr">
         <is>
           <t>bauteilart</t>
@@ -30598,7 +31172,11 @@
     </row>
     <row r="95" ht="13.5" customHeight="1" s="229">
       <c r="D95" s="55" t="n"/>
-      <c r="E95" s="55" t="n"/>
+      <c r="E95" s="55" t="inlineStr">
+        <is>
+          <t>component-type</t>
+        </is>
+      </c>
       <c r="F95" s="55" t="inlineStr">
         <is>
           <t>bauteiltyp</t>
@@ -30686,7 +31264,11 @@
     </row>
     <row r="96" ht="13.5" customHeight="1" s="229">
       <c r="D96" s="55" t="n"/>
-      <c r="E96" s="55" t="n"/>
+      <c r="E96" s="55" t="inlineStr">
+        <is>
+          <t>component-name</t>
+        </is>
+      </c>
       <c r="F96" s="55" t="inlineStr">
         <is>
           <t>bauteilname</t>
@@ -30770,7 +31352,11 @@
     </row>
     <row r="97" ht="13.5" customHeight="1" s="229">
       <c r="D97" s="55" t="n"/>
-      <c r="E97" s="55" t="n"/>
+      <c r="E97" s="55" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
       <c r="F97" s="55" t="inlineStr">
         <is>
           <t>hersteller</t>
@@ -30858,7 +31444,11 @@
     </row>
     <row r="98" ht="13.5" customHeight="1" s="229">
       <c r="D98" s="55" t="n"/>
-      <c r="E98" s="55" t="n"/>
+      <c r="E98" s="55" t="inlineStr">
+        <is>
+          <t>product-id</t>
+        </is>
+      </c>
       <c r="F98" s="55" t="inlineStr">
         <is>
           <t>produkt-id</t>
@@ -30946,7 +31536,11 @@
     </row>
     <row r="99" ht="13.5" customHeight="1" s="229">
       <c r="D99" s="55" t="n"/>
-      <c r="E99" s="55" t="n"/>
+      <c r="E99" s="55" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
+      </c>
       <c r="F99" s="55" t="inlineStr">
         <is>
           <t>material</t>
@@ -31026,7 +31620,11 @@
     </row>
     <row r="100" ht="13.5" customHeight="1" s="229">
       <c r="D100" s="55" t="n"/>
-      <c r="E100" s="55" t="n"/>
+      <c r="E100" s="55" t="inlineStr">
+        <is>
+          <t>serial-number</t>
+        </is>
+      </c>
       <c r="F100" s="55" t="inlineStr">
         <is>
           <t>seriennummer</t>
@@ -31114,7 +31712,11 @@
     </row>
     <row r="101" ht="13.5" customHeight="1" s="229">
       <c r="D101" s="55" t="n"/>
-      <c r="E101" s="55" t="n"/>
+      <c r="E101" s="55" t="inlineStr">
+        <is>
+          <t>asset-condition</t>
+        </is>
+      </c>
       <c r="F101" s="55" t="inlineStr">
         <is>
           <t>anlagenzustand</t>
@@ -31198,7 +31800,11 @@
     </row>
     <row r="102" ht="13.5" customHeight="1" s="229">
       <c r="D102" s="55" t="n"/>
-      <c r="E102" s="55" t="n"/>
+      <c r="E102" s="55" t="inlineStr">
+        <is>
+          <t>acquisition-cost</t>
+        </is>
+      </c>
       <c r="F102" s="55" t="inlineStr">
         <is>
           <t>anschaffungskosten</t>
@@ -31278,7 +31884,11 @@
     </row>
     <row r="103" ht="13.5" customHeight="1" s="229">
       <c r="D103" s="55" t="n"/>
-      <c r="E103" s="55" t="n"/>
+      <c r="E103" s="55" t="inlineStr">
+        <is>
+          <t>fire-protection-class</t>
+        </is>
+      </c>
       <c r="F103" s="55" t="inlineStr">
         <is>
           <t>brandschutzklasse</t>
@@ -31362,7 +31972,11 @@
     </row>
     <row r="104" ht="13.5" customHeight="1" s="229">
       <c r="D104" s="55" t="n"/>
-      <c r="E104" s="55" t="n"/>
+      <c r="E104" s="55" t="inlineStr">
+        <is>
+          <t>ebkp-h</t>
+        </is>
+      </c>
       <c r="F104" s="55" t="inlineStr">
         <is>
           <t>ebkp-h</t>
@@ -31442,7 +32056,11 @@
     </row>
     <row r="105" ht="13.5" customHeight="1" s="229">
       <c r="D105" s="55" t="n"/>
-      <c r="E105" s="55" t="n"/>
+      <c r="E105" s="55" t="inlineStr">
+        <is>
+          <t>burglar-resistance-class</t>
+        </is>
+      </c>
       <c r="F105" s="55" t="inlineStr">
         <is>
           <t>einbruchschutzklasse</t>
@@ -31526,7 +32144,11 @@
     </row>
     <row r="106" ht="13.5" customHeight="1" s="229">
       <c r="D106" s="55" t="n"/>
-      <c r="E106" s="55" t="n"/>
+      <c r="E106" s="55" t="inlineStr">
+        <is>
+          <t>escape-route-function</t>
+        </is>
+      </c>
       <c r="F106" s="55" t="inlineStr">
         <is>
           <t>fluchtwegfunktion</t>
@@ -31606,7 +32228,11 @@
     </row>
     <row r="107" ht="13.5" customHeight="1" s="229">
       <c r="D107" s="55" t="n"/>
-      <c r="E107" s="55" t="n"/>
+      <c r="E107" s="55" t="inlineStr">
+        <is>
+          <t>service-life</t>
+        </is>
+      </c>
       <c r="F107" s="55" t="inlineStr">
         <is>
           <t>lebensdauer</t>
@@ -31694,7 +32320,11 @@
     </row>
     <row r="108" ht="13.5" customHeight="1" s="229">
       <c r="D108" s="55" t="n"/>
-      <c r="E108" s="55" t="n"/>
+      <c r="E108" s="55" t="inlineStr">
+        <is>
+          <t>door-control</t>
+        </is>
+      </c>
       <c r="F108" s="55" t="inlineStr">
         <is>
           <t>tursteuerung</t>
@@ -31778,7 +32408,11 @@
     </row>
     <row r="109" ht="13.5" customHeight="1" s="229">
       <c r="D109" s="55" t="n"/>
-      <c r="E109" s="55" t="n"/>
+      <c r="E109" s="55" t="inlineStr">
+        <is>
+          <t>maintenance-contract</t>
+        </is>
+      </c>
       <c r="F109" s="55" t="inlineStr">
         <is>
           <t>wartungsvertrag</t>
@@ -31866,7 +32500,11 @@
     </row>
     <row r="110" ht="13.5" customHeight="1" s="229">
       <c r="D110" s="55" t="n"/>
-      <c r="E110" s="55" t="n"/>
+      <c r="E110" s="55" t="inlineStr">
+        <is>
+          <t>maintenance-interval</t>
+        </is>
+      </c>
       <c r="F110" s="55" t="inlineStr">
         <is>
           <t>wartungsintervall</t>
@@ -31954,7 +32592,11 @@
     </row>
     <row r="111" ht="13.5" customHeight="1" s="229">
       <c r="D111" s="55" t="n"/>
-      <c r="E111" s="55" t="n"/>
+      <c r="E111" s="55" t="inlineStr">
+        <is>
+          <t>acceptance-date</t>
+        </is>
+      </c>
       <c r="F111" s="55" t="inlineStr">
         <is>
           <t>abnahmedatum</t>
@@ -32034,7 +32676,11 @@
     </row>
     <row r="112" ht="13.5" customHeight="1" s="229">
       <c r="D112" s="55" t="n"/>
-      <c r="E112" s="55" t="n"/>
+      <c r="E112" s="55" t="inlineStr">
+        <is>
+          <t>commissioning-date</t>
+        </is>
+      </c>
       <c r="F112" s="55" t="inlineStr">
         <is>
           <t>inbetriebnahme</t>
@@ -32122,7 +32768,11 @@
     </row>
     <row r="113" ht="13.5" customHeight="1" s="229">
       <c r="D113" s="55" t="n"/>
-      <c r="E113" s="55" t="n"/>
+      <c r="E113" s="55" t="inlineStr">
+        <is>
+          <t>live-load</t>
+        </is>
+      </c>
       <c r="F113" s="55" t="inlineStr">
         <is>
           <t>nutzlast</t>
@@ -32206,7 +32856,11 @@
     </row>
     <row r="114" ht="13.5" customHeight="1" s="229">
       <c r="D114" s="55" t="n"/>
-      <c r="E114" s="55" t="n"/>
+      <c r="E114" s="55" t="inlineStr">
+        <is>
+          <t>window-type</t>
+        </is>
+      </c>
       <c r="F114" s="55" t="inlineStr">
         <is>
           <t>fensterart</t>
@@ -32286,7 +32940,11 @@
     </row>
     <row r="115" ht="13.5" customHeight="1" s="229">
       <c r="D115" s="55" t="n"/>
-      <c r="E115" s="55" t="n"/>
+      <c r="E115" s="55" t="inlineStr">
+        <is>
+          <t>locking-type</t>
+        </is>
+      </c>
       <c r="F115" s="55" t="inlineStr">
         <is>
           <t>schliessart</t>
@@ -32370,7 +33028,11 @@
     </row>
     <row r="116" ht="13.5" customHeight="1" s="229">
       <c r="D116" s="55" t="n"/>
-      <c r="E116" s="55" t="n"/>
+      <c r="E116" s="55" t="inlineStr">
+        <is>
+          <t>raised-floor</t>
+        </is>
+      </c>
       <c r="F116" s="55" t="inlineStr">
         <is>
           <t>doppelboden</t>
@@ -36414,7 +37076,11 @@
     </row>
     <row r="7" ht="56.25" customFormat="1" customHeight="1" s="189">
       <c r="D7" s="90" t="n"/>
-      <c r="E7" s="214" t="n"/>
+      <c r="E7" s="214" t="inlineStr">
+        <is>
+          <t>kbob-dk-fm-i14y-csv</t>
+        </is>
+      </c>
       <c r="F7" s="214" t="n"/>
       <c r="G7" s="42" t="inlineStr">
         <is>
@@ -37360,7 +38026,11 @@
     <row r="7" ht="33.75" customFormat="1" customHeight="1" s="189">
       <c r="A7" s="105" t="n"/>
       <c r="C7" s="105" t="n"/>
-      <c r="D7" s="112" t="n"/>
+      <c r="D7" s="112" t="inlineStr">
+        <is>
+          <t>kbob-grundstuck-architekt</t>
+        </is>
+      </c>
       <c r="E7" s="112" t="inlineStr">
         <is>
           <t>KBOB_Grundstuck_Architekt</t>
@@ -37402,7 +38072,11 @@
     <row r="8" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A8" s="105" t="n"/>
       <c r="C8" s="105" t="n"/>
-      <c r="D8" s="112" t="n"/>
+      <c r="D8" s="112" t="inlineStr">
+        <is>
+          <t>kbob-gebaude-architekt</t>
+        </is>
+      </c>
       <c r="E8" s="112" t="inlineStr">
         <is>
           <t>KBOB_Gebaude_Architekt</t>
@@ -37444,7 +38118,11 @@
     <row r="9" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A9" s="105" t="n"/>
       <c r="C9" s="105" t="n"/>
-      <c r="D9" s="112" t="n"/>
+      <c r="D9" s="112" t="inlineStr">
+        <is>
+          <t>kbob-gebaude-betriebfm</t>
+        </is>
+      </c>
       <c r="E9" s="112" t="inlineStr">
         <is>
           <t>KBOB_Gebaude_BetriebFM</t>
@@ -37486,7 +38164,11 @@
     <row r="10" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A10" s="105" t="n"/>
       <c r="C10" s="105" t="n"/>
-      <c r="D10" s="112" t="n"/>
+      <c r="D10" s="112" t="inlineStr">
+        <is>
+          <t>kbob-geschoss-architekt</t>
+        </is>
+      </c>
       <c r="E10" s="112" t="inlineStr">
         <is>
           <t>KBOB_Geschoss_Architekt</t>
@@ -37528,7 +38210,11 @@
     <row r="11" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A11" s="105" t="n"/>
       <c r="C11" s="105" t="n"/>
-      <c r="D11" s="53" t="n"/>
+      <c r="D11" s="53" t="inlineStr">
+        <is>
+          <t>kbob-geschoss-betriebfm</t>
+        </is>
+      </c>
       <c r="E11" s="53" t="inlineStr">
         <is>
           <t>KBOB_Geschoss_BetriebFM</t>
@@ -37570,7 +38256,11 @@
     <row r="12" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A12" s="105" t="n"/>
       <c r="C12" s="105" t="n"/>
-      <c r="D12" s="53" t="n"/>
+      <c r="D12" s="53" t="inlineStr">
+        <is>
+          <t>kbob-raum-architekt</t>
+        </is>
+      </c>
       <c r="E12" s="53" t="inlineStr">
         <is>
           <t>KBOB_Raum_Architekt</t>
@@ -37612,7 +38302,11 @@
     <row r="13" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A13" s="105" t="n"/>
       <c r="C13" s="105" t="n"/>
-      <c r="D13" s="53" t="n"/>
+      <c r="D13" s="53" t="inlineStr">
+        <is>
+          <t>kbob-raum-betriebfm</t>
+        </is>
+      </c>
       <c r="E13" s="53" t="inlineStr">
         <is>
           <t>KBOB_Raum_BetriebFM</t>
@@ -37654,7 +38348,11 @@
     <row r="14" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A14" s="105" t="n"/>
       <c r="C14" s="105" t="n"/>
-      <c r="D14" s="53" t="n"/>
+      <c r="D14" s="53" t="inlineStr">
+        <is>
+          <t>kbob-raum-hlkksse</t>
+        </is>
+      </c>
       <c r="E14" s="53" t="inlineStr">
         <is>
           <t>KBOB_Raum_HLKKSSE</t>
@@ -37696,7 +38394,11 @@
     <row r="15" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A15" s="105" t="n"/>
       <c r="C15" s="105" t="n"/>
-      <c r="D15" s="53" t="n"/>
+      <c r="D15" s="53" t="inlineStr">
+        <is>
+          <t>kbob-bauteil-hlkkssearchitekt</t>
+        </is>
+      </c>
       <c r="E15" s="53" t="inlineStr">
         <is>
           <t>KBOB_Bauteil_HLKKSSEArchitekt</t>
@@ -37738,7 +38440,11 @@
     <row r="16" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A16" s="105" t="n"/>
       <c r="C16" s="105" t="n"/>
-      <c r="D16" s="53" t="n"/>
+      <c r="D16" s="53" t="inlineStr">
+        <is>
+          <t>kbob-bauteil-hlkksse</t>
+        </is>
+      </c>
       <c r="E16" s="53" t="inlineStr">
         <is>
           <t>KBOB_Bauteil_HLKKSSE</t>
@@ -37780,7 +38486,11 @@
     <row r="17" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A17" s="105" t="n"/>
       <c r="C17" s="105" t="n"/>
-      <c r="D17" s="53" t="n"/>
+      <c r="D17" s="53" t="inlineStr">
+        <is>
+          <t>kbob-bauteil-architekt</t>
+        </is>
+      </c>
       <c r="E17" s="53" t="inlineStr">
         <is>
           <t>KBOB_Bauteil_Architekt</t>
@@ -37822,7 +38532,11 @@
     <row r="18" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A18" s="105" t="n"/>
       <c r="C18" s="105" t="n"/>
-      <c r="D18" s="53" t="n"/>
+      <c r="D18" s="53" t="inlineStr">
+        <is>
+          <t>kbob-bauteil-betriebfm</t>
+        </is>
+      </c>
       <c r="E18" s="53" t="inlineStr">
         <is>
           <t>KBOB_Bauteil_BetriebFM</t>
@@ -37864,7 +38578,11 @@
     <row r="19" ht="12.75" customFormat="1" customHeight="1" s="68">
       <c r="A19" s="105" t="n"/>
       <c r="C19" s="105" t="n"/>
-      <c r="D19" s="53" t="n"/>
+      <c r="D19" s="53" t="inlineStr">
+        <is>
+          <t>kbob-bauteil-elektroplaner</t>
+        </is>
+      </c>
       <c r="E19" s="53" t="inlineStr">
         <is>
           <t>KBOB_Bauteil_Elektroplaner</t>

--- a/templates/Strukturvorlage_DataDictionary_KBOB_FM_v0.9.5.xlsx
+++ b/templates/Strukturvorlage_DataDictionary_KBOB_FM_v0.9.5.xlsx
@@ -2400,7 +2400,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="26.140625" customWidth="1" style="229" min="1" max="1"/>
-    <col width="1.7109375" customWidth="1" style="229" min="2" max="2"/>
+    <col width="28" customWidth="1" style="229" min="2" max="2"/>
     <col width="31.7109375" bestFit="1" customWidth="1" style="229" min="3" max="3"/>
     <col width="1.7109375" customWidth="1" style="229" min="4" max="4"/>
     <col width="8.140625" customWidth="1" style="229" min="5" max="5"/>
@@ -2429,7 +2429,11 @@
   <sheetData>
     <row r="1" ht="17.65" customHeight="1" s="229">
       <c r="A1" s="194" t="n"/>
-      <c r="B1" s="194" t="n"/>
+      <c r="B1" s="35" t="inlineStr">
+        <is>
+          <t>Data Templates</t>
+        </is>
+      </c>
       <c r="C1" s="35" t="inlineStr">
         <is>
           <t>GoP</t>
@@ -2582,7 +2586,11 @@
     </row>
     <row r="2" ht="163.5" customHeight="1" s="229">
       <c r="A2" s="194" t="n"/>
-      <c r="B2" s="194" t="n"/>
+      <c r="B2" s="85" t="inlineStr">
+        <is>
+          <t>DataTemplate-ID</t>
+        </is>
+      </c>
       <c r="C2" s="85" t="inlineStr">
         <is>
           <t>GoP - Designation/Bezeichnung/Désignation/Designazione</t>
@@ -3207,7 +3215,11 @@
           <t>Classes</t>
         </is>
       </c>
-      <c r="B3" s="84" t="n"/>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>Stable identity</t>
+        </is>
+      </c>
       <c r="C3" s="194" t="n"/>
       <c r="D3" s="84" t="n"/>
       <c r="E3" s="194" t="n"/>
@@ -3344,7 +3356,11 @@
           <t>Class - Designation/Bezeichnung/Désignation/Designazione</t>
         </is>
       </c>
-      <c r="B4" s="195" t="n"/>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>Repeat the same ID across rows to attach 0..n GroupOfProperties</t>
+        </is>
+      </c>
       <c r="C4" s="196" t="n"/>
       <c r="D4" s="195" t="n"/>
       <c r="E4" s="196" t="n"/>
@@ -3485,7 +3501,11 @@
           <t>Grundstück</t>
         </is>
       </c>
-      <c r="B5" s="84" t="n"/>
+      <c r="B5" s="84" t="inlineStr">
+        <is>
+          <t>grundstueck-dt</t>
+        </is>
+      </c>
       <c r="C5" s="88" t="inlineStr">
         <is>
           <t>KBOB_Grundstuck_Architekt</t>
@@ -3666,7 +3686,11 @@
           <t>Grundstück</t>
         </is>
       </c>
-      <c r="B6" s="84" t="n"/>
+      <c r="B6" s="84" t="inlineStr">
+        <is>
+          <t>grundstueck-dt</t>
+        </is>
+      </c>
       <c r="C6" s="88" t="n"/>
       <c r="D6" s="84" t="n"/>
       <c r="E6" s="87" t="n"/>
@@ -3875,7 +3899,11 @@
           <t>Gebäude</t>
         </is>
       </c>
-      <c r="B7" s="91" t="n"/>
+      <c r="B7" s="91" t="inlineStr">
+        <is>
+          <t>gebaeude-dt</t>
+        </is>
+      </c>
       <c r="C7" s="42" t="inlineStr">
         <is>
           <t>KBOB_Gebaude_Architekt</t>
@@ -4044,7 +4072,11 @@
           <t>Gebäude</t>
         </is>
       </c>
-      <c r="B8" s="91" t="n"/>
+      <c r="B8" s="91" t="inlineStr">
+        <is>
+          <t>gebaeude-dt</t>
+        </is>
+      </c>
       <c r="C8" s="42" t="n"/>
       <c r="D8" s="91" t="n"/>
       <c r="E8" s="92" t="n"/>
@@ -4285,7 +4317,11 @@
           <t>Gebäude</t>
         </is>
       </c>
-      <c r="B9" s="91" t="n"/>
+      <c r="B9" s="91" t="inlineStr">
+        <is>
+          <t>gebaeude-dt</t>
+        </is>
+      </c>
       <c r="C9" s="42" t="inlineStr">
         <is>
           <t>KBOB_Gebaude_BetriebFM</t>
@@ -4474,7 +4510,11 @@
           <t>Geschoss</t>
         </is>
       </c>
-      <c r="B10" s="91" t="n"/>
+      <c r="B10" s="91" t="inlineStr">
+        <is>
+          <t>geschoss-dt</t>
+        </is>
+      </c>
       <c r="C10" s="42" t="inlineStr">
         <is>
           <t>KBOB_Geschoss_Architekt</t>
@@ -4655,7 +4695,11 @@
           <t>Geschoss</t>
         </is>
       </c>
-      <c r="B11" s="91" t="n"/>
+      <c r="B11" s="91" t="inlineStr">
+        <is>
+          <t>geschoss-dt</t>
+        </is>
+      </c>
       <c r="C11" s="42" t="n"/>
       <c r="D11" s="91" t="n"/>
       <c r="E11" s="92" t="n"/>
@@ -4840,7 +4884,11 @@
           <t>Geschoss</t>
         </is>
       </c>
-      <c r="B12" s="91" t="n"/>
+      <c r="B12" s="91" t="inlineStr">
+        <is>
+          <t>geschoss-dt</t>
+        </is>
+      </c>
       <c r="C12" s="93" t="inlineStr">
         <is>
           <t>KBOB_Geschoss_BetriebFM</t>
@@ -5013,7 +5061,11 @@
           <t>Raum</t>
         </is>
       </c>
-      <c r="B13" s="91" t="n"/>
+      <c r="B13" s="91" t="inlineStr">
+        <is>
+          <t>raum-dt</t>
+        </is>
+      </c>
       <c r="C13" s="93" t="inlineStr">
         <is>
           <t>KBOB_Raum_Architekt</t>
@@ -5226,7 +5278,11 @@
           <t>Raum</t>
         </is>
       </c>
-      <c r="B14" s="91" t="n"/>
+      <c r="B14" s="91" t="inlineStr">
+        <is>
+          <t>raum-dt</t>
+        </is>
+      </c>
       <c r="C14" s="93" t="inlineStr">
         <is>
           <t>KBOB_Raum_BetriebFM</t>
@@ -5407,7 +5463,11 @@
           <t>Raum</t>
         </is>
       </c>
-      <c r="B15" s="91" t="n"/>
+      <c r="B15" s="91" t="inlineStr">
+        <is>
+          <t>raum-dt</t>
+        </is>
+      </c>
       <c r="C15" s="93" t="n"/>
       <c r="D15" s="91" t="n"/>
       <c r="E15" s="92" t="n"/>
@@ -5660,7 +5720,11 @@
           <t>Raum</t>
         </is>
       </c>
-      <c r="B16" s="91" t="n"/>
+      <c r="B16" s="91" t="inlineStr">
+        <is>
+          <t>raum-dt</t>
+        </is>
+      </c>
       <c r="C16" s="93" t="inlineStr">
         <is>
           <t>KBOB_Raum_HLKKSSE</t>
@@ -5833,7 +5897,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B17" s="91" t="n"/>
+      <c r="B17" s="91" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C17" s="93" t="inlineStr">
         <is>
           <t>KBOB_Bauteil_HLKKSSEArchitekt</t>
@@ -6026,7 +6094,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B18" s="91" t="n"/>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C18" s="93" t="inlineStr">
         <is>
           <t>KBOB_Bauteil_HLKKSSE</t>
@@ -6219,7 +6291,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B19" s="91" t="n"/>
+      <c r="B19" s="91" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C19" s="93" t="n"/>
       <c r="D19" s="91" t="n"/>
       <c r="E19" s="92" t="n"/>
@@ -6432,7 +6508,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B20" s="91" t="n"/>
+      <c r="B20" s="91" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C20" s="93" t="inlineStr">
         <is>
           <t>KBOB_Bauteil_Architekt</t>
@@ -6617,7 +6697,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B21" s="91" t="n"/>
+      <c r="B21" s="91" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C21" s="93" t="inlineStr">
         <is>
           <t>KBOB_Bauteil_BetriebFM</t>
@@ -6798,7 +6882,11 @@
           <t>Bauteil</t>
         </is>
       </c>
-      <c r="B22" s="91" t="n"/>
+      <c r="B22" s="91" t="inlineStr">
+        <is>
+          <t>bauteil-dt</t>
+        </is>
+      </c>
       <c r="C22" s="93" t="inlineStr">
         <is>
           <t>KBOB_Bauteil_Elektroplaner</t>
